--- a/Methanol/Südafrika_Methanol_3_Bio_Brownfield/Datenbank.xlsx
+++ b/Methanol/Südafrika_Methanol_3_Bio_Brownfield/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Südafrika_Methanol_3_Bio_Brownfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E80EBCB-FC4B-4E1B-A67E-9118951F4D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F00A41-E34E-45AF-8F1E-584D4A5403FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-6945" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="386">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1324,6 +1324,12 @@
   </si>
   <si>
     <t>kg</t>
+  </si>
+  <si>
+    <t>Landesspezifischer Zinssatz</t>
+  </si>
+  <si>
+    <t>wacc_change</t>
   </si>
 </sst>
 </file>
@@ -1869,24 +1875,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G77"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="6"/>
+    <col min="11" max="11" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>69</v>
       </c>
@@ -1907,7 +1913,7 @@
       </c>
       <c r="G1" s="23"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="33" t="s">
         <v>70</v>
       </c>
@@ -1927,7 +1933,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="34"/>
       <c r="B3" s="41"/>
       <c r="C3" s="6" t="s">
@@ -1943,7 +1949,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="34"/>
       <c r="B4" s="41"/>
       <c r="C4" s="6" t="s">
@@ -1959,7 +1965,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="34"/>
       <c r="B5" s="41"/>
       <c r="C5" s="6" t="s">
@@ -1975,7 +1981,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="34"/>
       <c r="B6" s="41"/>
       <c r="C6" s="6" t="s">
@@ -1991,7 +1997,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="34"/>
       <c r="B7" s="41"/>
       <c r="C7" s="6" t="s">
@@ -2007,7 +2013,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="34"/>
       <c r="B8" s="44" t="s">
         <v>227</v>
@@ -2025,7 +2031,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="34"/>
       <c r="B9" s="41"/>
       <c r="C9" s="6" t="s">
@@ -2041,7 +2047,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="34"/>
       <c r="B10" s="41"/>
       <c r="C10" s="6" t="s">
@@ -2057,7 +2063,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="34"/>
       <c r="B11" s="41"/>
       <c r="C11" s="6" t="s">
@@ -2073,7 +2079,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="34"/>
       <c r="B12" s="41"/>
       <c r="C12" s="6" t="s">
@@ -2089,7 +2095,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="34"/>
       <c r="B13" s="41"/>
       <c r="C13" s="6" t="s">
@@ -2105,7 +2111,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="34"/>
       <c r="B14" s="41"/>
       <c r="C14" s="6" t="s">
@@ -2121,7 +2127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="34"/>
       <c r="B15" s="45"/>
       <c r="C15" s="15" t="s">
@@ -2137,7 +2143,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="34"/>
       <c r="B16" s="44" t="s">
         <v>269</v>
@@ -2155,7 +2161,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="34"/>
       <c r="B17" s="41"/>
       <c r="C17" s="6" t="s">
@@ -2171,7 +2177,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="34"/>
       <c r="B18" s="41"/>
       <c r="C18" s="6" t="s">
@@ -2187,7 +2193,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="34"/>
       <c r="B19" s="41"/>
       <c r="C19" s="6" t="s">
@@ -2203,7 +2209,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="34"/>
       <c r="B20" s="41"/>
       <c r="C20" s="6" t="s">
@@ -2219,7 +2225,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="34"/>
       <c r="B21" s="45"/>
       <c r="C21" s="15" t="s">
@@ -2235,7 +2241,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="34"/>
       <c r="B22" s="37" t="s">
         <v>336</v>
@@ -2253,7 +2259,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="34"/>
       <c r="B23" s="37"/>
       <c r="C23" s="6" t="s">
@@ -2269,7 +2275,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="34"/>
       <c r="B24" s="37"/>
       <c r="C24" s="6" t="s">
@@ -2285,7 +2291,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="34"/>
       <c r="B25" s="37"/>
       <c r="C25" s="6" t="s">
@@ -2301,7 +2307,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="34"/>
       <c r="B26" s="37"/>
       <c r="C26" s="6" t="s">
@@ -2317,7 +2323,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="34"/>
       <c r="B27" s="37"/>
       <c r="C27" s="6" t="s">
@@ -2333,7 +2339,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="34"/>
       <c r="B28" s="37"/>
       <c r="C28" s="6" t="s">
@@ -2349,7 +2355,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="34"/>
       <c r="B29" s="37"/>
       <c r="C29" s="6" t="s">
@@ -2365,7 +2371,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="34"/>
       <c r="B30" s="37"/>
       <c r="C30" s="6" t="s">
@@ -2381,7 +2387,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="33" t="s">
         <v>71</v>
       </c>
@@ -2401,7 +2407,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="34"/>
       <c r="B32" s="37"/>
       <c r="C32" s="6" t="s">
@@ -2417,7 +2423,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="34"/>
       <c r="B33" s="37"/>
       <c r="C33" s="6" t="s">
@@ -2433,7 +2439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="34"/>
       <c r="B34" s="37"/>
       <c r="C34" s="6" t="s">
@@ -2449,7 +2455,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="34"/>
       <c r="B35" s="37"/>
       <c r="C35" s="6" t="s">
@@ -2465,7 +2471,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="34"/>
       <c r="B36" s="37"/>
       <c r="C36" s="6" t="s">
@@ -2481,7 +2487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="34"/>
       <c r="B37" s="37"/>
       <c r="C37" s="6" t="s">
@@ -2497,7 +2503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="34"/>
       <c r="B38" s="38"/>
       <c r="C38" s="15" t="s">
@@ -2513,7 +2519,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="34"/>
       <c r="B39" s="39" t="s">
         <v>311</v>
@@ -2531,7 +2537,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="34"/>
       <c r="B40" s="37"/>
       <c r="C40" s="6" t="s">
@@ -2547,7 +2553,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="34"/>
       <c r="B41" s="37"/>
       <c r="C41" s="6" t="s">
@@ -2563,7 +2569,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="34"/>
       <c r="B42" s="37"/>
       <c r="C42" s="6" t="s">
@@ -2579,7 +2585,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="34"/>
       <c r="B43" s="37"/>
       <c r="C43" s="6" t="s">
@@ -2595,7 +2601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="34"/>
       <c r="B44" s="37"/>
       <c r="C44" s="6" t="s">
@@ -2611,7 +2617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="34"/>
       <c r="B45" s="37"/>
       <c r="C45" s="6" t="s">
@@ -2627,7 +2633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="34"/>
       <c r="B46" s="37"/>
       <c r="C46" s="15" t="s">
@@ -2643,7 +2649,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="34"/>
       <c r="B47" s="39" t="s">
         <v>201</v>
@@ -2661,7 +2667,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="34"/>
       <c r="B48" s="41"/>
       <c r="C48" s="6" t="s">
@@ -2678,7 +2684,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="34"/>
       <c r="B49" s="41"/>
       <c r="C49" s="6" t="s">
@@ -2694,7 +2700,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="34"/>
       <c r="B50" s="41"/>
       <c r="C50" s="6" t="s">
@@ -2710,7 +2716,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="34"/>
       <c r="B51" s="41"/>
       <c r="C51" s="6" t="s">
@@ -2726,7 +2732,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="34"/>
       <c r="B52" s="41"/>
       <c r="C52" s="6" t="s">
@@ -2742,7 +2748,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="34"/>
       <c r="B53" s="41"/>
       <c r="C53" s="6" t="s">
@@ -2758,7 +2764,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="34"/>
       <c r="B54" s="41"/>
       <c r="C54" s="6" t="s">
@@ -2774,7 +2780,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="34"/>
       <c r="B55" s="41"/>
       <c r="C55" s="6" t="s">
@@ -2790,7 +2796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="35"/>
       <c r="B56" s="42"/>
       <c r="C56" s="19" t="s">
@@ -2806,7 +2812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="33" t="s">
         <v>72</v>
       </c>
@@ -2826,7 +2832,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="34"/>
       <c r="B58" s="32" t="s">
         <v>337</v>
@@ -2844,7 +2850,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="34"/>
       <c r="B59" s="39" t="s">
         <v>4</v>
@@ -2862,7 +2868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="34"/>
       <c r="B60" s="37"/>
       <c r="C60" s="6" t="s">
@@ -2878,7 +2884,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="34"/>
       <c r="B61" s="37"/>
       <c r="C61" s="6" t="s">
@@ -2894,7 +2900,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="34"/>
       <c r="B62" s="37"/>
       <c r="C62" s="6" t="s">
@@ -2910,7 +2916,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="34"/>
       <c r="B63" s="37"/>
       <c r="C63" s="6" t="s">
@@ -2926,7 +2932,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="34"/>
       <c r="B64" s="37"/>
       <c r="C64" s="6" t="s">
@@ -2942,7 +2948,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="34"/>
       <c r="B65" s="38"/>
       <c r="C65" s="15" t="s">
@@ -2958,7 +2964,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="34"/>
       <c r="B66" s="39" t="s">
         <v>5</v>
@@ -2976,7 +2982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="34"/>
       <c r="B67" s="37"/>
       <c r="C67" s="6" t="s">
@@ -2992,7 +2998,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="34"/>
       <c r="B68" s="37"/>
       <c r="C68" s="6" t="s">
@@ -3008,7 +3014,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="34"/>
       <c r="B69" s="37"/>
       <c r="C69" s="6" t="s">
@@ -3024,7 +3030,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="34"/>
       <c r="B70" s="37"/>
       <c r="C70" s="6" t="s">
@@ -3040,7 +3046,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="34"/>
       <c r="B71" s="37"/>
       <c r="C71" s="6" t="s">
@@ -3056,7 +3062,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="35"/>
       <c r="B72" s="40"/>
       <c r="C72" s="19" t="s">
@@ -3072,7 +3078,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="33" t="s">
         <v>76</v>
       </c>
@@ -3092,7 +3098,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="34"/>
       <c r="B74" s="23" t="s">
         <v>295</v>
@@ -3110,7 +3116,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="34"/>
       <c r="B75" s="28" t="s">
         <v>79</v>
@@ -3128,7 +3134,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="35"/>
       <c r="B76" s="4" t="s">
         <v>258</v>
@@ -3144,6 +3150,26 @@
       </c>
       <c r="F76" s="19" t="s">
         <v>271</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E77" s="11">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3171,18 +3197,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F147"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="6"/>
+    <col min="1" max="1" width="14.54296875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="6" customWidth="1"/>
+    <col min="7" max="16384" width="11.54296875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>69</v>
       </c>
@@ -3202,7 +3228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="33" t="s">
         <v>70</v>
       </c>
@@ -3220,7 +3246,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="34"/>
       <c r="B3" s="41"/>
       <c r="C3" s="6" t="s">
@@ -3234,7 +3260,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="34"/>
       <c r="B4" s="41"/>
       <c r="C4" s="6" t="s">
@@ -3248,7 +3274,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="34"/>
       <c r="B5" s="41"/>
       <c r="C5" s="6" t="s">
@@ -3262,7 +3288,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="34"/>
       <c r="B6" s="41"/>
       <c r="C6" s="6" t="s">
@@ -3276,7 +3302,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="34"/>
       <c r="B7" s="41"/>
       <c r="C7" s="6" t="s">
@@ -3290,7 +3316,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="34"/>
       <c r="B8" s="41"/>
       <c r="C8" s="6" t="s">
@@ -3304,7 +3330,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="34"/>
       <c r="B9" s="41"/>
       <c r="C9" s="6" t="s">
@@ -3318,7 +3344,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="34"/>
       <c r="B10" s="41"/>
       <c r="C10" s="6" t="s">
@@ -3332,12 +3358,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="34"/>
       <c r="B11" s="41"/>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="34"/>
       <c r="B12" s="44" t="s">
         <v>227</v>
@@ -3353,7 +3379,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="34"/>
       <c r="B13" s="41"/>
       <c r="C13" s="6" t="s">
@@ -3367,7 +3393,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="34"/>
       <c r="B14" s="41"/>
       <c r="C14" s="6" t="s">
@@ -3381,7 +3407,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="34"/>
       <c r="B15" s="41"/>
       <c r="C15" s="6" t="s">
@@ -3395,7 +3421,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="34"/>
       <c r="B16" s="41"/>
       <c r="C16" s="6" t="s">
@@ -3409,7 +3435,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="34"/>
       <c r="B17" s="41"/>
       <c r="C17" s="6" t="s">
@@ -3423,7 +3449,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="34"/>
       <c r="B18" s="41"/>
       <c r="C18" s="6" t="s">
@@ -3437,7 +3463,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="34"/>
       <c r="B19" s="41"/>
       <c r="C19" s="6" t="s">
@@ -3451,7 +3477,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="34"/>
       <c r="B20" s="41"/>
       <c r="C20" s="6" t="s">
@@ -3465,7 +3491,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="34"/>
       <c r="B21" s="41"/>
       <c r="C21" s="6" t="s">
@@ -3479,7 +3505,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="34"/>
       <c r="B22" s="45"/>
       <c r="C22" s="15"/>
@@ -3487,7 +3513,7 @@
       <c r="E22" s="16"/>
       <c r="F22" s="15"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="34"/>
       <c r="B23" s="44" t="s">
         <v>269</v>
@@ -3503,7 +3529,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="34"/>
       <c r="B24" s="41"/>
       <c r="C24" s="6" t="s">
@@ -3517,7 +3543,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="34"/>
       <c r="B25" s="41"/>
       <c r="C25" s="6" t="s">
@@ -3531,7 +3557,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="34"/>
       <c r="B26" s="41"/>
       <c r="C26" s="6" t="s">
@@ -3545,7 +3571,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="34"/>
       <c r="B27" s="41"/>
       <c r="C27" s="6" t="s">
@@ -3559,7 +3585,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="34"/>
       <c r="B28" s="41"/>
       <c r="C28" s="6" t="s">
@@ -3573,7 +3599,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="34"/>
       <c r="B29" s="41"/>
       <c r="C29" s="6" t="s">
@@ -3587,7 +3613,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="34"/>
       <c r="B30" s="41"/>
       <c r="C30" s="6" t="s">
@@ -3601,7 +3627,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="34"/>
       <c r="B31" s="41"/>
       <c r="C31" s="6" t="s">
@@ -3615,7 +3641,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="34"/>
       <c r="B32" s="45"/>
       <c r="C32" s="15"/>
@@ -3623,7 +3649,7 @@
       <c r="E32" s="16"/>
       <c r="F32" s="15"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="34"/>
       <c r="B33" s="37" t="s">
         <v>354</v>
@@ -3639,7 +3665,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="34"/>
       <c r="B34" s="37"/>
       <c r="C34" s="6" t="s">
@@ -3653,7 +3679,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="34"/>
       <c r="B35" s="37"/>
       <c r="C35" s="6" t="s">
@@ -3667,7 +3693,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="34"/>
       <c r="B36" s="37"/>
       <c r="C36" s="6" t="s">
@@ -3681,7 +3707,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="34"/>
       <c r="B37" s="37"/>
       <c r="C37" s="6" t="s">
@@ -3695,7 +3721,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="34"/>
       <c r="B38" s="37"/>
       <c r="C38" s="6" t="s">
@@ -3709,7 +3735,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="34"/>
       <c r="B39" s="37"/>
       <c r="C39" s="6" t="s">
@@ -3723,7 +3749,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="34"/>
       <c r="B40" s="37"/>
       <c r="C40" s="6" t="s">
@@ -3737,7 +3763,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="34"/>
       <c r="B41" s="37"/>
       <c r="C41" s="6" t="s">
@@ -3751,7 +3777,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="34"/>
       <c r="B42" s="37"/>
       <c r="C42" s="6" t="s">
@@ -3765,7 +3791,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="34"/>
       <c r="B43" s="37"/>
       <c r="C43" s="6" t="s">
@@ -3779,7 +3805,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="34"/>
       <c r="B44" s="37"/>
       <c r="C44" s="6" t="s">
@@ -3793,12 +3819,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="34"/>
       <c r="B45" s="37"/>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="33" t="s">
         <v>71</v>
       </c>
@@ -3816,7 +3842,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="34"/>
       <c r="B47" s="37"/>
       <c r="C47" s="6" t="s">
@@ -3830,7 +3856,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="34"/>
       <c r="B48" s="37"/>
       <c r="C48" s="6" t="s">
@@ -3844,7 +3870,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="34"/>
       <c r="B49" s="37"/>
       <c r="C49" s="6" t="s">
@@ -3858,7 +3884,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="34"/>
       <c r="B50" s="37"/>
       <c r="C50" s="6" t="s">
@@ -3872,7 +3898,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="34"/>
       <c r="B51" s="37"/>
       <c r="C51" s="6" t="s">
@@ -3886,7 +3912,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="34"/>
       <c r="B52" s="37"/>
       <c r="C52" s="6" t="s">
@@ -3900,7 +3926,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="34"/>
       <c r="B53" s="37"/>
       <c r="C53" s="6" t="s">
@@ -3914,7 +3940,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="34"/>
       <c r="B54" s="37"/>
       <c r="C54" s="6" t="s">
@@ -3928,7 +3954,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="34"/>
       <c r="B55" s="38"/>
       <c r="C55" s="15"/>
@@ -3936,7 +3962,7 @@
       <c r="E55" s="16"/>
       <c r="F55" s="15"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="34"/>
       <c r="B56" s="37" t="s">
         <v>311</v>
@@ -3952,7 +3978,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="34"/>
       <c r="B57" s="37"/>
       <c r="C57" s="6" t="s">
@@ -3966,7 +3992,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="34"/>
       <c r="B58" s="37"/>
       <c r="C58" s="6" t="s">
@@ -3980,7 +4006,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="34"/>
       <c r="B59" s="37"/>
       <c r="C59" s="6" t="s">
@@ -3994,7 +4020,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="34"/>
       <c r="B60" s="37"/>
       <c r="C60" s="6" t="s">
@@ -4008,7 +4034,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="34"/>
       <c r="B61" s="37"/>
       <c r="C61" s="6" t="s">
@@ -4022,7 +4048,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="34"/>
       <c r="B62" s="37"/>
       <c r="C62" s="6" t="s">
@@ -4036,7 +4062,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="34"/>
       <c r="B63" s="37"/>
       <c r="C63" s="6" t="s">
@@ -4050,7 +4076,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="34"/>
       <c r="B64" s="37"/>
       <c r="C64" s="6" t="s">
@@ -4064,12 +4090,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="34"/>
       <c r="B65" s="38"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="34"/>
       <c r="B66" s="39" t="s">
         <v>6</v>
@@ -4085,7 +4111,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="34"/>
       <c r="B67" s="37"/>
       <c r="C67" s="6" t="s">
@@ -4099,7 +4125,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="34"/>
       <c r="B68" s="41"/>
       <c r="C68" s="6" t="s">
@@ -4113,7 +4139,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="34"/>
       <c r="B69" s="41"/>
       <c r="C69" s="6" t="s">
@@ -4127,7 +4153,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="34"/>
       <c r="B70" s="41"/>
       <c r="C70" s="6" t="s">
@@ -4141,7 +4167,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="34"/>
       <c r="B71" s="41"/>
       <c r="C71" s="6" t="s">
@@ -4155,7 +4181,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="34"/>
       <c r="B72" s="41"/>
       <c r="C72" s="6" t="s">
@@ -4169,7 +4195,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="34"/>
       <c r="B73" s="41"/>
       <c r="C73" s="6" t="s">
@@ -4183,7 +4209,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="34"/>
       <c r="B74" s="41"/>
       <c r="C74" s="6" t="s">
@@ -4197,7 +4223,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="34"/>
       <c r="B75" s="41"/>
       <c r="C75" s="6" t="s">
@@ -4211,7 +4237,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="34"/>
       <c r="B76" s="41"/>
       <c r="C76" s="6" t="s">
@@ -4225,7 +4251,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="35"/>
       <c r="B77" s="42"/>
       <c r="C77" s="19"/>
@@ -4233,7 +4259,7 @@
       <c r="E77" s="20"/>
       <c r="F77" s="19"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="33" t="s">
         <v>72</v>
       </c>
@@ -4251,7 +4277,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="34"/>
       <c r="B79" s="41"/>
       <c r="C79" s="6" t="s">
@@ -4265,7 +4291,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="34"/>
       <c r="B80" s="45"/>
       <c r="C80" s="15"/>
@@ -4273,7 +4299,7 @@
       <c r="E80" s="21"/>
       <c r="F80" s="15"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="34"/>
       <c r="B81" s="41" t="s">
         <v>337</v>
@@ -4289,7 +4315,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="34"/>
       <c r="B82" s="41"/>
       <c r="C82" s="6" t="s">
@@ -4303,12 +4329,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="34"/>
       <c r="B83" s="41"/>
       <c r="E83" s="9"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="34"/>
       <c r="B84" s="39" t="s">
         <v>4</v>
@@ -4324,7 +4350,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="34"/>
       <c r="B85" s="37"/>
       <c r="C85" s="6" t="s">
@@ -4338,7 +4364,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="34"/>
       <c r="B86" s="37"/>
       <c r="C86" s="6" t="s">
@@ -4352,7 +4378,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="34"/>
       <c r="B87" s="37"/>
       <c r="C87" s="6" t="s">
@@ -4366,7 +4392,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="34"/>
       <c r="B88" s="37"/>
       <c r="C88" s="6" t="s">
@@ -4380,7 +4406,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="34"/>
       <c r="B89" s="37"/>
       <c r="C89" s="6" t="s">
@@ -4394,7 +4420,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="34"/>
       <c r="B90" s="37"/>
       <c r="C90" s="6" t="s">
@@ -4408,7 +4434,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="34"/>
       <c r="B91" s="37"/>
       <c r="C91" s="6" t="s">
@@ -4422,7 +4448,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="34"/>
       <c r="B92" s="37"/>
       <c r="C92" s="6" t="s">
@@ -4436,11 +4462,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="34"/>
       <c r="B93" s="38"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="34"/>
       <c r="B94" s="39" t="s">
         <v>5</v>
@@ -4456,7 +4482,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="34"/>
       <c r="B95" s="37"/>
       <c r="C95" s="6" t="s">
@@ -4470,7 +4496,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="34"/>
       <c r="B96" s="37"/>
       <c r="C96" s="6" t="s">
@@ -4484,7 +4510,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="34"/>
       <c r="B97" s="37"/>
       <c r="C97" s="6" t="s">
@@ -4498,7 +4524,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="34"/>
       <c r="B98" s="37"/>
       <c r="C98" s="6" t="s">
@@ -4512,7 +4538,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="34"/>
       <c r="B99" s="37"/>
       <c r="C99" s="6" t="s">
@@ -4526,7 +4552,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="34"/>
       <c r="B100" s="37"/>
       <c r="C100" s="6" t="s">
@@ -4540,7 +4566,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="34"/>
       <c r="B101" s="37"/>
       <c r="C101" s="6" t="s">
@@ -4554,7 +4580,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="34"/>
       <c r="B102" s="37"/>
       <c r="C102" s="6" t="s">
@@ -4568,11 +4594,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="35"/>
       <c r="B103" s="40"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="33" t="s">
         <v>76</v>
       </c>
@@ -4590,7 +4616,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="34"/>
       <c r="B105" s="41"/>
       <c r="C105" s="6" t="s">
@@ -4604,7 +4630,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="34"/>
       <c r="B106" s="45"/>
       <c r="C106" s="15"/>
@@ -4612,7 +4638,7 @@
       <c r="E106" s="16"/>
       <c r="F106" s="15"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="34"/>
       <c r="B107" s="44" t="s">
         <v>299</v>
@@ -4628,7 +4654,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="34"/>
       <c r="B108" s="41"/>
       <c r="C108" s="6" t="s">
@@ -4642,12 +4668,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="34"/>
       <c r="B109" s="45"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="34"/>
       <c r="B110" s="44" t="s">
         <v>79</v>
@@ -4663,7 +4689,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="34"/>
       <c r="B111" s="41"/>
       <c r="C111" s="6" t="s">
@@ -4677,7 +4703,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="34"/>
       <c r="B112" s="45"/>
       <c r="C112" s="15"/>
@@ -4685,7 +4711,7 @@
       <c r="E112" s="16"/>
       <c r="F112" s="15"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="34"/>
       <c r="B113" s="44" t="s">
         <v>258</v>
@@ -4701,7 +4727,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="34"/>
       <c r="B114" s="41"/>
       <c r="C114" s="6" t="s">
@@ -4715,7 +4741,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="35"/>
       <c r="B115" s="42"/>
       <c r="C115" s="19"/>
@@ -4723,7 +4749,7 @@
       <c r="E115" s="20"/>
       <c r="F115" s="19"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="33" t="s">
         <v>163</v>
       </c>
@@ -4741,7 +4767,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="34"/>
       <c r="B117" s="41"/>
       <c r="C117" s="6" t="s">
@@ -4754,7 +4780,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="34"/>
       <c r="B118" s="45"/>
       <c r="C118" s="15"/>
@@ -4762,7 +4788,7 @@
       <c r="E118" s="15"/>
       <c r="F118" s="15"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="34"/>
       <c r="B119" s="44" t="s">
         <v>183</v>
@@ -4777,7 +4803,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="34"/>
       <c r="B120" s="41"/>
       <c r="C120" s="6" t="s">
@@ -4790,7 +4816,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="34"/>
       <c r="B121" s="41"/>
       <c r="C121" s="6" t="s">
@@ -4803,7 +4829,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="34"/>
       <c r="B122" s="41"/>
       <c r="C122" s="6" t="s">
@@ -4816,7 +4842,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="34"/>
       <c r="B123" s="41"/>
       <c r="C123" s="6" t="s">
@@ -4829,7 +4855,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="34"/>
       <c r="B124" s="41"/>
       <c r="C124" s="6" t="s">
@@ -4842,11 +4868,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="34"/>
       <c r="B125" s="41"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="34"/>
       <c r="B126" s="44" t="s">
         <v>206</v>
@@ -4862,7 +4888,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="34"/>
       <c r="B127" s="41"/>
       <c r="C127" s="6" t="s">
@@ -4875,7 +4901,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="34"/>
       <c r="B128" s="41"/>
       <c r="C128" s="6" t="s">
@@ -4888,7 +4914,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="34"/>
       <c r="B129" s="41"/>
       <c r="C129" s="6" t="s">
@@ -4901,7 +4927,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="34"/>
       <c r="B130" s="41"/>
       <c r="C130" s="6" t="s">
@@ -4914,7 +4940,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="34"/>
       <c r="B131" s="41"/>
       <c r="C131" s="6" t="s">
@@ -4927,7 +4953,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="34"/>
       <c r="B132" s="41"/>
       <c r="C132" s="6" t="s">
@@ -4940,7 +4966,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="34"/>
       <c r="B133" s="41"/>
       <c r="C133" s="6" t="s">
@@ -4953,7 +4979,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="34"/>
       <c r="B134" s="41"/>
       <c r="C134" s="6" t="s">
@@ -4966,7 +4992,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="34"/>
       <c r="B135" s="41"/>
       <c r="C135" s="6" t="s">
@@ -4979,7 +5005,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="34"/>
       <c r="B136" s="41"/>
       <c r="C136" s="6" t="s">
@@ -4992,7 +5018,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="34"/>
       <c r="B137" s="41"/>
       <c r="C137" s="6" t="s">
@@ -5005,11 +5031,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="34"/>
       <c r="B138" s="41"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="34"/>
       <c r="B139" s="44" t="s">
         <v>222</v>
@@ -5025,7 +5051,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="34"/>
       <c r="B140" s="41"/>
       <c r="C140" s="6" t="s">
@@ -5038,7 +5064,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="34"/>
       <c r="B141" s="41"/>
       <c r="C141" s="6" t="s">
@@ -5051,7 +5077,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="34"/>
       <c r="B142" s="41"/>
       <c r="C142" s="6" t="s">
@@ -5064,7 +5090,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="34"/>
       <c r="B143" s="41"/>
       <c r="C143" s="6" t="s">
@@ -5077,11 +5103,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="34"/>
       <c r="B144" s="45"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="34"/>
       <c r="B145" s="44" t="s">
         <v>376</v>
@@ -5097,7 +5123,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="34"/>
       <c r="B146" s="41"/>
       <c r="C146" s="6" t="s">
@@ -5110,20 +5136,11 @@
         <v>271</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="A78:A103"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="B94:B103"/>
-    <mergeCell ref="A104:A115"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B78:B80"/>
     <mergeCell ref="B145:B146"/>
     <mergeCell ref="B139:B144"/>
     <mergeCell ref="A116:A147"/>
@@ -5140,6 +5157,15 @@
     <mergeCell ref="B113:B115"/>
     <mergeCell ref="B119:B125"/>
     <mergeCell ref="B126:B138"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A115"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B78:B80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
